--- a/CONVOCATORIA ESPECIALISTA_ProyectoOrion/ConvEspProyAnexosConv5.xlsx
+++ b/CONVOCATORIA ESPECIALISTA_ProyectoOrion/ConvEspProyAnexosConv5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\inf_sri\CONVOCATORIA ESPECIALISTA_ProyectoOrion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A95B3F-3051-4080-BAFB-B6FA406084DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281828D5-3299-4654-A541-D3D172FB1617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" xr2:uid="{E783ACA3-A0C3-4028-B60F-C242B1BF5F06}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="159">
   <si>
     <t>#</t>
   </si>
@@ -369,16 +369,9 @@
 NO TIENE EXPERIENCIA EN DESARROLLO</t>
   </si>
   <si>
-    <t>Paola Granda</t>
-  </si>
-  <si>
     <t>0985517196</t>
   </si>
   <si>
-    <t>CENTRAL
-REVISAR EXPERIENCIA</t>
-  </si>
-  <si>
     <t>0402037592</t>
   </si>
   <si>
@@ -392,10 +385,6 @@
   </si>
   <si>
     <t>0960400373</t>
-  </si>
-  <si>
-    <t>POLITECNICA ESTATAL DEL CARCHI
-NO INDICA EXPERIENCIA EN JAVA</t>
   </si>
   <si>
     <t xml:space="preserve">UNACH
@@ -512,6 +501,57 @@
   </si>
   <si>
     <t>Se solicitó informacion completa</t>
+  </si>
+  <si>
+    <t>BYRON FRANCISCO SOLIZ ACOSTA</t>
+  </si>
+  <si>
+    <t>francisco-soliz@hotmail.com</t>
+  </si>
+  <si>
+    <t>0991917102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TECNOLOGO en artes </t>
+  </si>
+  <si>
+    <t>POLITECNICA ESTATAL DEL CARCHI
+Obtuvo el titulo el 2021-08-12</t>
+  </si>
+  <si>
+    <t>0995 592 380</t>
+  </si>
+  <si>
+    <t>edison.palomino@hotmail.com</t>
+  </si>
+  <si>
+    <t>PALOMINO LANDETA EDISON ABRAHAM</t>
+  </si>
+  <si>
+    <t>Tecnologo desde 2015
+Ingenieria registrada el 2026-05-26</t>
+  </si>
+  <si>
+    <t>GRANDA VINUEZA PAOLA ELIZABETH</t>
+  </si>
+  <si>
+    <t>CENTRAL
+EXPERIENCIA EN DATOS LA MAS ACTUAL</t>
+  </si>
+  <si>
+    <t>Coello Quezada Ricardo</t>
+  </si>
+  <si>
+    <t>PORRAS JUMBO JHONNATAN DANIEL</t>
+  </si>
+  <si>
+    <t>Obtiene el título de ingeniero en : 2026-09-07</t>
+  </si>
+  <si>
+    <t>jhonnatanporras23@gmail.com</t>
+  </si>
+  <si>
+    <t>0958806224</t>
   </si>
 </sst>
 </file>
@@ -3442,7 +3482,7 @@
         <v>83</v>
       </c>
       <c r="F2" s="93" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>90</v>
@@ -3451,7 +3491,7 @@
     <row r="3" spans="1:8" ht="43.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D3" s="84" t="s">
         <v>85</v>
@@ -3460,7 +3500,7 @@
         <v>84</v>
       </c>
       <c r="F3" s="93" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>86</v>
@@ -3469,7 +3509,7 @@
     <row r="4" spans="1:8" ht="51" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C4" s="92"/>
       <c r="D4" s="84" t="s">
@@ -3488,7 +3528,7 @@
     <row r="5" spans="1:8" ht="28.8" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C5" s="92">
         <v>1724216195</v>
@@ -3500,7 +3540,7 @@
         <v>92</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>86</v>
@@ -3521,7 +3561,7 @@
         <v>95</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>86</v>
@@ -3530,7 +3570,7 @@
     <row r="7" spans="1:8" ht="28.8">
       <c r="A7" s="2"/>
       <c r="B7" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C7" s="92">
         <v>1715760763</v>
@@ -3551,7 +3591,7 @@
     <row r="8" spans="1:8" ht="43.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C8" s="92">
         <v>1316327707</v>
@@ -3572,17 +3612,19 @@
     <row r="9" spans="1:8" ht="28.8">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="92">
+        <v>1716533284</v>
+      </c>
+      <c r="D9" s="84" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="94" t="s">
-        <v>103</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>90</v>
@@ -3591,19 +3633,19 @@
     <row r="10" spans="1:8" ht="28.8">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C10" s="92" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="92" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="84" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" s="92" t="s">
-        <v>107</v>
-      </c>
       <c r="F10" s="5" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>90</v>
@@ -3612,19 +3654,19 @@
     <row r="11" spans="1:8" ht="43.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C11" s="92">
         <v>1724718182</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E11" s="92" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>86</v>
@@ -3633,19 +3675,19 @@
     <row r="12" spans="1:8" ht="28.8">
       <c r="A12" s="2"/>
       <c r="B12" s="132" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C12" s="132">
         <v>1717376808</v>
       </c>
       <c r="D12" s="80" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E12" s="133" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>90</v>
@@ -3654,19 +3696,19 @@
     <row r="13" spans="1:8" ht="28.8">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C13" s="92">
         <v>1719224766</v>
       </c>
       <c r="D13" s="84" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E13" s="92" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>90</v>
@@ -3675,17 +3717,17 @@
     <row r="14" spans="1:8" ht="28.8">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C14" s="92"/>
       <c r="D14" s="84" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E14" s="92" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>86</v>
@@ -3694,19 +3736,19 @@
     <row r="15" spans="1:8">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="243" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="84" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="243" t="s">
+      <c r="F15" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="D15" s="84" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" s="92" t="s">
-        <v>138</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>86</v>
@@ -3715,49 +3757,85 @@
     <row r="16" spans="1:8" ht="28.8">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="84" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E16" s="92" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F16" s="93" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="B17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1721415113</v>
+      </c>
+      <c r="D17" s="84" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="92" t="s">
+        <v>145</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="28.8">
       <c r="A18" s="2"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1713983839</v>
+      </c>
+      <c r="D18" s="84" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" s="92" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="B19" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1727403865</v>
+      </c>
+      <c r="D19" s="84" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="92" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2"/>
@@ -4286,9 +4364,12 @@
     <hyperlink ref="D9" r:id="rId10" xr:uid="{172DF7E6-4B9E-4CF3-A7D3-303E305E70C2}"/>
     <hyperlink ref="D15" r:id="rId11" xr:uid="{ACECF861-C304-4084-8D43-D36AED2C8838}"/>
     <hyperlink ref="D16" r:id="rId12" xr:uid="{12D4F734-7FF6-45EF-8F07-E118297CB824}"/>
+    <hyperlink ref="D17" r:id="rId13" xr:uid="{DF04A76E-2D5B-43A8-8897-BAB62A783E0C}"/>
+    <hyperlink ref="D18" r:id="rId14" xr:uid="{FF34C18F-1922-4187-96A7-B6CC5CEC9A19}"/>
+    <hyperlink ref="D19" r:id="rId15" xr:uid="{C1AC0ADB-28A1-4DFC-94C1-F33FBE5D843F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -4517,7 +4598,9 @@
       </c>
     </row>
     <row r="8" spans="1:32" ht="14.4" customHeight="1">
-      <c r="A8" s="300"/>
+      <c r="A8" s="300" t="s">
+        <v>154</v>
+      </c>
       <c r="B8" s="167"/>
       <c r="C8" s="168"/>
       <c r="D8" s="168"/>
